--- a/data/trans_orig/IP07A08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A08-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20966</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>23529</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>34529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>26327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37739</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70521</t>
+          <t>70747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16450</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29333</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>27139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22032</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31191</t>
+          <t>31754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43569</t>
+          <t>44918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32223</t>
+          <t>31263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>40863</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>28506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34661</t>
+          <t>34981</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49172</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17607</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23053</t>
+          <t>23280</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>35756</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>28511</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>40568</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32969</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>45205</t>
+          <t>45033</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>65090</t>
+          <t>65302</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>82064</t>
+          <t>81993</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27735</t>
+          <t>27436</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>31508</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>47536</t>
+          <t>47285</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>45521</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>36375</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>49389</t>
+          <t>49802</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>71516</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>90995</t>
+          <t>92056</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>40637</t>
+          <t>40847</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>34827</t>
+          <t>34476</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>51942</t>
+          <t>51784</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>71422</t>
+          <t>71398</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>156476</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>186549</t>
+          <t>187675</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>173491</t>
+          <t>171764</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>203150</t>
+          <t>201130</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>338134</t>
+          <t>338003</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>378401</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>118213</t>
+          <t>117367</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>148109</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>125080</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>154384</t>
+          <t>154784</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>253439</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>293464</t>
+          <t>294176</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>23945</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>23276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42852</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29718</t>
+          <t>30475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39568</t>
+          <t>39604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35743</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46040</t>
+          <t>45901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69093</t>
+          <t>69789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82903</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>18353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40732</t>
+          <t>41813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>25913</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>427</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>34801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>20735</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34952</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38683</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>73144</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29692</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>53632</t>
+          <t>53819</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>47803</t>
+          <t>47421</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>43108</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>65045</t>
+          <t>66096</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>86414</t>
+          <t>87553</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>55,01%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>43165</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>30808</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44693</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>61643</t>
+          <t>62739</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>83383</t>
+          <t>83270</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>175415</t>
+          <t>176647</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>204360</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>174190</t>
+          <t>173078</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>202715</t>
+          <t>202939</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,47 +12612,47 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
+          <t>61,03%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>378656</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>357244</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>399052</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>54,59%</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
           <t>60,97%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>378656</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>358158</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>398169</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>107566</t>
+          <t>106485</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>134727</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>112876</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>142749</t>
+          <t>141458</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>229339</t>
+          <t>228213</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>267692</t>
+          <t>269308</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>27865</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>42078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>24524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47036</t>
+          <t>47565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>41233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50982</t>
+          <t>50948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81135</t>
+          <t>81770</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96507</t>
+          <t>96181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>26731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>22832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23125</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28657</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43732</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35252</t>
+          <t>35088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>29477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>59628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71643</t>
+          <t>72018</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,47 +15767,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5087</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2143</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5698</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27203</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>37157</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32506</t>
+          <t>32080</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21635</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>46167</t>
+          <t>44777</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>64879</t>
+          <t>64863</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>43967</t>
+          <t>43548</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>26918</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>60886</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>79840</t>
+          <t>80452</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,83%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>37833</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>36883</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>70469</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>35797</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>50394</t>
+          <t>49867</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>38592</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>52607</t>
+          <t>52875</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>78929</t>
+          <t>78473</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>99834</t>
+          <t>98690</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>173857</t>
+          <t>173862</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>204970</t>
+          <t>207589</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>185330</t>
+          <t>185167</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>217812</t>
+          <t>216944</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>370818</t>
+          <t>368485</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>413054</t>
+          <t>416148</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>132538</t>
+          <t>129555</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>161904</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>129991</t>
+          <t>131102</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>162502</t>
+          <t>162355</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>271021</t>
+          <t>270428</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>314186</t>
+          <t>315271</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
